--- a/public/exports-60-250/29189439.xlsx
+++ b/public/exports-60-250/29189439.xlsx
@@ -5629,12 +5629,12 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5704,12 +5704,12 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
